--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7160,6 +7160,512 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132053798</v>
+      </c>
+      <c r="B59" t="n">
+        <v>96354</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Söder om Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>585587</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6375613</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132053611</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Söder om Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>585606</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6375568</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132053635</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91861</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Söder om Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>585654</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6375504</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132053588</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Söder om Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>585575</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6375568</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132053575</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90863</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Söder om Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>585633</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6375537</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96354</v>
+        <v>96355</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91861</v>
+        <v>91862</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90863</v>
+        <v>90864</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96355</v>
+        <v>96360</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B61" t="n">
-        <v>91862</v>
+        <v>91846</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B62" t="n">
-        <v>91841</v>
+        <v>91867</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90864</v>
+        <v>90869</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91846</v>
+        <v>91867</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R61" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91867</v>
+        <v>91846</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R62" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96360</v>
+        <v>96362</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B61" t="n">
-        <v>91867</v>
+        <v>91848</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B62" t="n">
-        <v>91846</v>
+        <v>91869</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90869</v>
+        <v>90871</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91848</v>
+        <v>91869</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R61" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91869</v>
+        <v>91848</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R62" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B61" t="n">
-        <v>91869</v>
+        <v>91848</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B62" t="n">
-        <v>91848</v>
+        <v>91869</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96362</v>
+        <v>96398</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91869</v>
+        <v>91905</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90871</v>
+        <v>90907</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91889</v>
+        <v>91913</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R61" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91910</v>
+        <v>91892</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R62" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90912</v>
+        <v>90915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B61" t="n">
-        <v>91913</v>
+        <v>91892</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B62" t="n">
-        <v>91892</v>
+        <v>91913</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91892</v>
+        <v>91919</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R61" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91913</v>
+        <v>91898</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R62" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90915</v>
+        <v>90921</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B61" t="n">
-        <v>91919</v>
+        <v>91898</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B62" t="n">
-        <v>91898</v>
+        <v>91919</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91898</v>
+        <v>91929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R61" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91919</v>
+        <v>91908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R62" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90921</v>
+        <v>90931</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B61" t="n">
-        <v>91929</v>
+        <v>91908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B62" t="n">
-        <v>91908</v>
+        <v>91929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96424</v>
+        <v>96426</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91908</v>
+        <v>91930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R61" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91929</v>
+        <v>91909</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R62" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90931</v>
+        <v>90932</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B61" t="n">
-        <v>91930</v>
+        <v>91909</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B62" t="n">
-        <v>91909</v>
+        <v>91930</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -7165,7 +7165,7 @@
         <v>132053798</v>
       </c>
       <c r="B59" t="n">
-        <v>96426</v>
+        <v>96427</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>132053611</v>
       </c>
       <c r="B60" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053588</v>
+        <v>132053635</v>
       </c>
       <c r="B61" t="n">
-        <v>91909</v>
+        <v>91931</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,21 +7373,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585575</v>
+        <v>585654</v>
       </c>
       <c r="R61" t="n">
-        <v>6375568</v>
+        <v>6375504</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053635</v>
+        <v>132053588</v>
       </c>
       <c r="B62" t="n">
-        <v>91930</v>
+        <v>91910</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,21 +7475,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585654</v>
+        <v>585575</v>
       </c>
       <c r="R62" t="n">
-        <v>6375504</v>
+        <v>6375568</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
         <v>132053575</v>
       </c>
       <c r="B63" t="n">
-        <v>90932</v>
+        <v>90933</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107132700</v>
+        <v>107133718</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>26</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585585.2350836834</v>
+        <v>585708</v>
       </c>
       <c r="R2" t="n">
-        <v>6375560.045249265</v>
+        <v>6375629</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107135056</v>
+        <v>107134538</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>26</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585638.9621626529</v>
+        <v>585608</v>
       </c>
       <c r="R3" t="n">
-        <v>6375513.895208263</v>
+        <v>6375602</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +859,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107132387</v>
+        <v>107144152</v>
       </c>
       <c r="B4" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,35 +882,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1639</v>
+        <v>26</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Flagmon, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585557.8791011532</v>
+        <v>585711</v>
       </c>
       <c r="R4" t="n">
-        <v>6375580.960862563</v>
+        <v>6375586</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,94 +942,75 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107133010</v>
+        <v>132053556</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585651.8510505015</v>
+        <v>585565</v>
       </c>
       <c r="R5" t="n">
-        <v>6375592.071985076</v>
+        <v>6375462</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,22 +1037,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,31 +1053,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>barrlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107134800</v>
+        <v>107132381</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,21 +1085,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585617.3485379536</v>
+        <v>585659</v>
       </c>
       <c r="R6" t="n">
-        <v>6375645.609964394</v>
+        <v>6375435</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,22 +1140,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,37 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107133655</v>
+        <v>107132528</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585712.196392988</v>
+        <v>585695</v>
       </c>
       <c r="R7" t="n">
-        <v>6375640.622821463</v>
+        <v>6375445</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,22 +1248,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,56 +1278,47 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107136170</v>
+        <v>107133796</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585695.5953097988</v>
+        <v>585598</v>
       </c>
       <c r="R8" t="n">
-        <v>6375636.512196906</v>
+        <v>6375580</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1435,19 +1359,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,54 +1388,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107136357</v>
+        <v>107140166</v>
       </c>
       <c r="B9" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1639</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>A 10600, V Ramnebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585701.609614714</v>
+        <v>585582</v>
       </c>
       <c r="R9" t="n">
-        <v>6375606.551767148</v>
+        <v>6375598</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,19 +1467,14 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granlåga med mkt ullticka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,69 +1483,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107132320</v>
+        <v>107143930</v>
       </c>
       <c r="B10" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Flagmon, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585630.4069520805</v>
+        <v>585584</v>
       </c>
       <c r="R10" t="n">
-        <v>6375459.986380638</v>
+        <v>6375600</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1658,22 +1570,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,33 +1594,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107133799</v>
+        <v>107132700</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585598.2690777029</v>
+        <v>585585</v>
       </c>
       <c r="R11" t="n">
-        <v>6375580.198701322</v>
+        <v>6375560</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1774,19 +1682,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,68 +1699,58 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107133954</v>
+        <v>107133530</v>
       </c>
       <c r="B12" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585708.6561727733</v>
+        <v>585675</v>
       </c>
       <c r="R12" t="n">
-        <v>6375629.802862079</v>
+        <v>6375638</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1892,19 +1780,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,15 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107140166</v>
+        <v>107133621</v>
       </c>
       <c r="B13" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,48 +1820,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 10600, V Ramnebo, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585581.7425130673</v>
+        <v>585604</v>
       </c>
       <c r="R13" t="n">
-        <v>6375598.118296827</v>
+        <v>6375594</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,60 +1878,39 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På granlåga med mkt ullticka</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107136452</v>
+        <v>107133666</v>
       </c>
       <c r="B14" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,21 +1918,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585731.2769650233</v>
+        <v>585719</v>
       </c>
       <c r="R14" t="n">
-        <v>6375578.164072688</v>
+        <v>6375635</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2134,19 +1976,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,37 +2005,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107136015</v>
+        <v>107133672</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2214,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585662.5127047487</v>
+        <v>585613</v>
       </c>
       <c r="R15" t="n">
-        <v>6375648.172567344</v>
+        <v>6375585</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2247,24 +2074,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>20-tal plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,37 +2103,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107135143</v>
+        <v>107133690</v>
       </c>
       <c r="B16" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1639</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2139,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585563.2270054767</v>
+        <v>585594</v>
       </c>
       <c r="R16" t="n">
-        <v>6375505.854207151</v>
+        <v>6375585</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2365,19 +2172,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,56 +2189,47 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107136049</v>
+        <v>107133799</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2449,10 +2237,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585675.4538795421</v>
+        <v>585598</v>
       </c>
       <c r="R17" t="n">
-        <v>6375621.581687463</v>
+        <v>6375580</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2482,19 +2270,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,27 +2287,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107136266</v>
+        <v>107134404</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,21 +2310,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2562,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585710.4916535425</v>
+        <v>585596</v>
       </c>
       <c r="R18" t="n">
-        <v>6375644.885042863</v>
+        <v>6375595</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2595,19 +2368,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,37 +2397,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107133685</v>
+        <v>107134709</v>
       </c>
       <c r="B19" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585713.6459446496</v>
+        <v>585617</v>
       </c>
       <c r="R19" t="n">
-        <v>6375622.923489145</v>
+        <v>6375646</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,19 +2466,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,49 +2483,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107133715</v>
+        <v>107135056</v>
       </c>
       <c r="B20" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2779</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2788,10 +2531,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585709.4607671447</v>
+        <v>585638</v>
       </c>
       <c r="R20" t="n">
-        <v>6375642.714253465</v>
+        <v>6375514</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2821,19 +2564,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,51 +2593,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107132841</v>
+        <v>107143957</v>
       </c>
       <c r="B21" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Flagmon, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585705.7255830301</v>
+        <v>585584</v>
       </c>
       <c r="R21" t="n">
-        <v>6375538.941626027</v>
+        <v>6375600</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2931,27 +2661,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2960,33 +2685,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107132381</v>
+        <v>115706424</v>
       </c>
       <c r="B22" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,35 +2715,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Flagmon, Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585658.919471303</v>
+        <v>585595</v>
       </c>
       <c r="R22" t="n">
-        <v>6375435.333867929</v>
+        <v>6375590</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3049,22 +2769,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,15 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107133690</v>
+        <v>132053588</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,17 +2830,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585593.8514334442</v>
+        <v>585575</v>
       </c>
       <c r="R23" t="n">
-        <v>6375585.478495727</v>
+        <v>6375568</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3162,22 +2866,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,31 +2882,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107132528</v>
+        <v>132053611</v>
       </c>
       <c r="B24" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,35 +2914,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585694.7685707369</v>
+        <v>585606</v>
       </c>
       <c r="R24" t="n">
-        <v>6375445.760129112</v>
+        <v>6375568</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3275,22 +2968,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,18 +2982,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3320,16 +3009,11 @@
         <v>107133624</v>
       </c>
       <c r="B25" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3358,10 +3042,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585717.6110738685</v>
+        <v>585717</v>
       </c>
       <c r="R25" t="n">
-        <v>6375639.125108128</v>
+        <v>6375639</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3391,19 +3075,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,37 +3104,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>107132382</v>
+        <v>107132387</v>
       </c>
       <c r="B26" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3471,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585658.919471303</v>
+        <v>585558</v>
       </c>
       <c r="R26" t="n">
-        <v>6375435.333867929</v>
+        <v>6375581</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3501,22 +3170,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,49 +3190,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>107136101</v>
+        <v>107133068</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1639</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3238,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585668.6059155324</v>
+        <v>585679</v>
       </c>
       <c r="R27" t="n">
-        <v>6375614.452954476</v>
+        <v>6375579</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3617,24 +3271,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,56 +3288,47 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>107136092</v>
+        <v>107135143</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1639</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3706,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585684.2731356274</v>
+        <v>585563</v>
       </c>
       <c r="R28" t="n">
-        <v>6375637.348238443</v>
+        <v>6375506</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3739,19 +3369,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3778,15 +3398,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>107136311</v>
+        <v>107136357</v>
       </c>
       <c r="B29" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3409,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2671</v>
+        <v>1639</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3819,10 +3434,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585707.0130218115</v>
+        <v>585702</v>
       </c>
       <c r="R29" t="n">
-        <v>6375605.59106</v>
+        <v>6375607</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3852,19 +3467,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3879,49 +3484,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>107133796</v>
+        <v>107136602</v>
       </c>
       <c r="B30" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1639</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3932,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585598.2690777029</v>
+        <v>585765</v>
       </c>
       <c r="R30" t="n">
-        <v>6375580.198701322</v>
+        <v>6375495</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3967,7 +3567,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3977,7 +3577,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4004,51 +3604,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107133621</v>
+        <v>107144048</v>
       </c>
       <c r="B31" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1639</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Flagmon, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585603.9054506603</v>
+        <v>585711</v>
       </c>
       <c r="R31" t="n">
-        <v>6375593.749154429</v>
+        <v>6375586</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4080,7 +3677,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4090,7 +3687,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4099,69 +3696,64 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107132809</v>
+        <v>132053575</v>
       </c>
       <c r="B32" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90997</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2810</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585705.7255830301</v>
+        <v>585633</v>
       </c>
       <c r="R32" t="n">
-        <v>6375538.941626027</v>
+        <v>6375537</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4188,22 +3780,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4214,31 +3796,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>107133718</v>
+        <v>84536654</v>
       </c>
       <c r="B33" t="n">
-        <v>90596</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4246,35 +3828,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>26</v>
+        <v>2590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585708.6561727733</v>
+        <v>585647</v>
       </c>
       <c r="R33" t="n">
-        <v>6375629.802862079</v>
+        <v>6375403</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4301,22 +3886,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4325,33 +3900,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad, Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>107133068</v>
+        <v>84536657</v>
       </c>
       <c r="B34" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,35 +3930,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1639</v>
+        <v>2590</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585679.0491117281</v>
+        <v>585574</v>
       </c>
       <c r="R34" t="n">
-        <v>6375578.675579439</v>
+        <v>6375455</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4414,22 +3988,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4438,55 +4002,51 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad, Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>107133666</v>
+        <v>107132041</v>
       </c>
       <c r="B35" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4497,10 +4057,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585719.3158230904</v>
+        <v>585581</v>
       </c>
       <c r="R35" t="n">
-        <v>6375634.862883409</v>
+        <v>6375443</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4527,22 +4087,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4557,49 +4117,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>107133672</v>
+        <v>107132074</v>
       </c>
       <c r="B36" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4610,10 +4165,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585613.2223307114</v>
+        <v>585559</v>
       </c>
       <c r="R36" t="n">
-        <v>6375585.886113201</v>
+        <v>6375457</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4640,22 +4195,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,51 +4237,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>107133530</v>
+        <v>115704912</v>
       </c>
       <c r="B37" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Flagmon, Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585674.5878082236</v>
+        <v>585587</v>
       </c>
       <c r="R37" t="n">
-        <v>6375637.144247952</v>
+        <v>6375511</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4753,22 +4302,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4783,63 +4322,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>107134404</v>
+        <v>132053703</v>
       </c>
       <c r="B38" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97471</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585595.8003601775</v>
+        <v>585565</v>
       </c>
       <c r="R38" t="n">
-        <v>6375595.190426837</v>
+        <v>6375462</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4866,22 +4399,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4896,65 +4419,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>107157384</v>
+        <v>132053714</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97862</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2606</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Flagmon, Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585667.2017950437</v>
+        <v>585655</v>
       </c>
       <c r="R39" t="n">
-        <v>6375630.004211631</v>
+        <v>6375398</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4978,27 +4496,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5007,33 +4510,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>107144178</v>
+        <v>107133685</v>
       </c>
       <c r="B40" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,20 +4563,17 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Flagmon, Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585712.9092489467</v>
+        <v>585713</v>
       </c>
       <c r="R40" t="n">
-        <v>6375606.789832629</v>
+        <v>6375622</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5102,93 +4603,78 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>107157385</v>
+        <v>107136311</v>
       </c>
       <c r="B41" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585655.9879908804</v>
+        <v>585706</v>
       </c>
       <c r="R41" t="n">
-        <v>6375651.258774079</v>
+        <v>6375606</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5217,7 +4703,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,12 +4713,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20-tal exemplar</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5247,54 +4728,50 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>107144143</v>
+        <v>107144178</v>
       </c>
       <c r="B42" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5302,10 +4779,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585711.1982201484</v>
+        <v>585713</v>
       </c>
       <c r="R42" t="n">
-        <v>6375585.800112586</v>
+        <v>6375607</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5335,19 +4812,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5375,56 +4842,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>107143957</v>
+        <v>107157389</v>
       </c>
       <c r="B43" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Flagmon, Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585583.8722319833</v>
+        <v>585705</v>
       </c>
       <c r="R43" t="n">
-        <v>6375599.237646179</v>
+        <v>6375632</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5451,55 +4910,39 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>107144152</v>
+        <v>107157390</v>
       </c>
       <c r="B44" t="n">
-        <v>90596</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,40 +4950,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>26</v>
+        <v>2671</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flagmon, Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585711.1982201484</v>
+        <v>585701</v>
       </c>
       <c r="R44" t="n">
-        <v>6375585.800112586</v>
+        <v>6375633</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5567,55 +5007,39 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>107144035</v>
+        <v>132053798</v>
       </c>
       <c r="B45" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,38 +5047,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>2671</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flagmon, Stora Ramm, Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585711.1982201484</v>
+        <v>585587</v>
       </c>
       <c r="R45" t="n">
-        <v>6375585.800112586</v>
+        <v>6375613</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5681,22 +5101,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5705,34 +5115,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>107157389</v>
+        <v>107133715</v>
       </c>
       <c r="B46" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5740,37 +5144,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585704.306318261</v>
+        <v>585709</v>
       </c>
       <c r="R46" t="n">
-        <v>6375631.86029357</v>
+        <v>6375643</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5797,19 +5202,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5824,27 +5219,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>107157390</v>
+        <v>107132809</v>
       </c>
       <c r="B47" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5852,37 +5242,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>2810</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585701.5933183468</v>
+        <v>585706</v>
       </c>
       <c r="R47" t="n">
-        <v>6375632.877674857</v>
+        <v>6375538</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5906,22 +5297,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5936,27 +5327,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>107143930</v>
+        <v>115704610</v>
       </c>
       <c r="B48" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5964,37 +5350,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Flagmon, Stora Ramm, Sm</t>
+          <t>Flagmon, Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585583.8722319833</v>
+        <v>585574</v>
       </c>
       <c r="R48" t="n">
-        <v>6375599.237646179</v>
+        <v>6375509</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6021,22 +5404,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6045,76 +5418,70 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>107144017</v>
+        <v>115918850</v>
       </c>
       <c r="B49" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flagmon, Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585720.7540908422</v>
+        <v>585690</v>
       </c>
       <c r="R49" t="n">
-        <v>6375617.700560106</v>
+        <v>6375503</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6138,22 +5505,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6162,34 +5529,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Martin Charlier</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
+          <t>Martin Charlier</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>107144048</v>
+        <v>107132320</v>
       </c>
       <c r="B50" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6197,37 +5558,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1639</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flagmon, Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585711.1982201484</v>
+        <v>585631</v>
       </c>
       <c r="R50" t="n">
-        <v>6375585.800112586</v>
+        <v>6375459</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6254,22 +5613,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6278,34 +5637,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>107157386</v>
+        <v>107132414</v>
       </c>
       <c r="B51" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6313,37 +5666,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585618.4517466719</v>
+        <v>585654</v>
       </c>
       <c r="R51" t="n">
-        <v>6375618.76977169</v>
+        <v>6375412</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6367,22 +5721,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6397,49 +5751,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>107134538</v>
+        <v>107135931</v>
       </c>
       <c r="B52" t="n">
-        <v>90596</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>26</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6450,10 +5799,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585608.0292642156</v>
+        <v>585686</v>
       </c>
       <c r="R52" t="n">
-        <v>6375602.432295865</v>
+        <v>6375665</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6483,19 +5832,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6510,27 +5849,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>115706424</v>
+        <v>107136452</v>
       </c>
       <c r="B53" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6538,34 +5872,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Flagmon (Flagmon), Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585595</v>
+        <v>585731</v>
       </c>
       <c r="R53" t="n">
-        <v>6375590</v>
+        <v>6375578</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6592,12 +5927,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6612,62 +5947,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>115704912</v>
+        <v>132053635</v>
       </c>
       <c r="B54" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2590</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flagmon (Flagmon), Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585587</v>
+        <v>585654</v>
       </c>
       <c r="R54" t="n">
-        <v>6375511</v>
+        <v>6375504</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6694,12 +6024,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6710,31 +6040,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>115704610</v>
+        <v>107133655</v>
       </c>
       <c r="B55" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6742,34 +6072,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Flagmon (Flagmon), Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585574</v>
+        <v>585713</v>
       </c>
       <c r="R55" t="n">
-        <v>6375509</v>
+        <v>6375641</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6796,12 +6127,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6816,62 +6147,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>115704763</v>
+        <v>132053724</v>
       </c>
       <c r="B56" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Flagmon (Flagmon), Sm</t>
+          <t>Söder om Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585571</v>
+        <v>585643</v>
       </c>
       <c r="R56" t="n">
-        <v>6375498</v>
+        <v>6375409</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6898,12 +6224,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6914,73 +6240,70 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>115918616</v>
+        <v>107132382</v>
       </c>
       <c r="B57" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585690</v>
+        <v>585659</v>
       </c>
       <c r="R57" t="n">
-        <v>6375503</v>
+        <v>6375435</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7004,22 +6327,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7034,69 +6357,61 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Charlier</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Charlier</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>115918850</v>
+        <v>107136266</v>
       </c>
       <c r="B58" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>585690</v>
+        <v>585711</v>
       </c>
       <c r="R58" t="n">
-        <v>6375503</v>
+        <v>6375644</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7120,22 +6435,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7150,57 +6465,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Charlier</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Charlier</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132053798</v>
+        <v>107144143</v>
       </c>
       <c r="B59" t="n">
-        <v>96427</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2671</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Söder om Stora Ramm, Sm</t>
+          <t>Flagmon, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>585587</v>
+        <v>585711</v>
       </c>
       <c r="R59" t="n">
-        <v>6375613</v>
+        <v>6375586</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7227,12 +6545,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7241,63 +6559,70 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132053611</v>
+        <v>107134978</v>
       </c>
       <c r="B60" t="n">
-        <v>91910</v>
+        <v>57141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Söder om Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>585606</v>
+        <v>585625</v>
       </c>
       <c r="R60" t="n">
-        <v>6375568</v>
+        <v>6375491</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7324,12 +6649,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7338,69 +6663,63 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132053635</v>
+        <v>115704763</v>
       </c>
       <c r="B61" t="n">
-        <v>91931</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Söder om Stora Ramm, Sm</t>
+          <t>Flagmon, Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585654</v>
+        <v>585571</v>
       </c>
       <c r="R61" t="n">
-        <v>6375504</v>
+        <v>6375498</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7427,12 +6746,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7443,66 +6762,62 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132053588</v>
+        <v>107132841</v>
       </c>
       <c r="B62" t="n">
-        <v>91910</v>
+        <v>5179</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Söder om Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585575</v>
+        <v>585706</v>
       </c>
       <c r="R62" t="n">
-        <v>6375568</v>
+        <v>6375538</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7529,12 +6844,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-03-04</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2023-03-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7545,66 +6875,67 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132053575</v>
+        <v>107133954</v>
       </c>
       <c r="B63" t="n">
-        <v>90933</v>
+        <v>5179</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Söder om Stora Ramm, Sm</t>
+          <t>Flagmon, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>585633</v>
+        <v>585708</v>
       </c>
       <c r="R63" t="n">
-        <v>6375537</v>
+        <v>6375629</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7631,12 +6962,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7647,24 +6978,1506 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>107157382</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>585646</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6375563</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>107133010</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>585652</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6375592</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>107136015</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>585662</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6375648</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>20-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>107136049</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>585676</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6375622</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>107136092</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>585685</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6375637</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>107136101</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>585669</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6375614</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>107136170</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>585695</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6375637</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>107157384</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>585668</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6375630</v>
+      </c>
+      <c r="S71" t="n">
+        <v>20</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>107157385</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>585656</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6375651</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>20-tal exemplar</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>115918616</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>585690</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6375503</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Martin Charlier</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Martin Charlier</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>107140140</v>
+      </c>
+      <c r="B74" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>A 10600, V Ramnebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>585549</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6375515</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>107144035</v>
+      </c>
+      <c r="B75" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Flagmon, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>585711</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6375586</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>107157386</v>
+      </c>
+      <c r="B76" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Flagmon, Sm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>585619</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6375618</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>107144017</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Flagmon, Stora Ramm, Sm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>585720</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6375618</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10600-2023 artfynd.xlsx
+++ b/artfynd/A 10600-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133718</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107134538</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107144152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053556</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132381</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132528</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133796</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140166</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107143930</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132700</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133621</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133666</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133672</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133690</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2296,6 +2376,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133799</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107134404</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107134709</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2590,6 +2685,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107135056</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107143957</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2798,6 +2903,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115706424</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053588</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3003,6 +3118,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053611</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3101,6 +3221,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133624</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3199,6 +3324,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132387</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3297,6 +3427,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133068</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3395,6 +3530,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107135143</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3493,6 +3633,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136357</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3601,6 +3746,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136602</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3712,6 +3862,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107144048</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3814,6 +3969,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053575</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3916,6 +4076,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84536654</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4018,6 +4183,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84536657</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4126,6 +4296,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132041</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4234,6 +4409,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132074</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4331,6 +4511,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115704912</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4428,6 +4613,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053703</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4531,6 +4721,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053714</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4629,6 +4824,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133685</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4737,6 +4937,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136311</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4839,6 +5044,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107144178</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4936,6 +5146,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107157389</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5033,6 +5248,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107157390</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5130,6 +5350,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053798</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5228,6 +5453,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133715</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5336,6 +5566,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132809</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5433,6 +5668,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115704610</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5544,6 +5784,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115918850</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5652,6 +5897,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132320</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5760,6 +6010,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132414</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5858,6 +6113,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107135931</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5956,6 +6216,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136452</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6058,6 +6323,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053635</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6156,6 +6426,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133655</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6258,6 +6533,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053724</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6366,6 +6646,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132382</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6474,6 +6759,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136266</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6575,6 +6865,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107144143</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6678,6 +6973,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107134978</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6775,6 +7075,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115704763</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6888,6 +7193,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107132841</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6991,6 +7301,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133954</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7088,6 +7403,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107157382</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7190,6 +7510,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107133010</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7303,6 +7628,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136015</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7405,6 +7735,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136049</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7507,6 +7842,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136092</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7620,6 +7960,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136101</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7732,6 +8077,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107136170</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7834,6 +8184,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107157384</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7936,6 +8291,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107157385</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8047,6 +8407,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115918616</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8157,6 +8522,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140140</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8269,6 +8639,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107144035</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8366,6 +8741,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107157386</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8478,8 +8858,91 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107144017</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>